--- a/outputs/factors/quality_returns.xlsx
+++ b/outputs/factors/quality_returns.xlsx
@@ -446,7 +446,7 @@
         <v>41333</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0.0003505160688425158</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +454,7 @@
         <v>41364</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.0007276708475944316</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         <v>41394</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001050324551129321</v>
+        <v>0.003795793500031102</v>
       </c>
     </row>
     <row r="5">
@@ -470,7 +470,7 @@
         <v>41425</v>
       </c>
       <c r="B5" t="n">
-        <v>5.109073702265818e-05</v>
+        <v>0.002914143800819856</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +478,7 @@
         <v>41455</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0.00321033251535626</v>
       </c>
     </row>
     <row r="7">
@@ -486,7 +486,7 @@
         <v>41486</v>
       </c>
       <c r="B7" t="n">
-        <v>0.002429315258463274</v>
+        <v>0.004129165072297688</v>
       </c>
     </row>
     <row r="8">
@@ -494,7 +494,7 @@
         <v>41517</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-0.001048906784669553</v>
       </c>
     </row>
     <row r="9">
@@ -502,7 +502,7 @@
         <v>41547</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001431957560462685</v>
+        <v>0.006230689823961966</v>
       </c>
     </row>
     <row r="10">
@@ -510,7 +510,7 @@
         <v>41578</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001768649893054411</v>
+        <v>0.003497552848327398</v>
       </c>
     </row>
     <row r="11">
@@ -518,7 +518,7 @@
         <v>41608</v>
       </c>
       <c r="B11" t="n">
-        <v>2.167788798593291e-05</v>
+        <v>0.002350034315336401</v>
       </c>
     </row>
     <row r="12">
@@ -526,7 +526,7 @@
         <v>41639</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0003822073351156436</v>
+        <v>0.003058654928036421</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>41670</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0005134009340455237</v>
+        <v>0.0009397731148197081</v>
       </c>
     </row>
     <row r="14">
@@ -542,7 +542,7 @@
         <v>41698</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.00546268623255154</v>
       </c>
     </row>
     <row r="15">
@@ -550,7 +550,7 @@
         <v>41729</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.00098779378412577</v>
       </c>
     </row>
     <row r="16">
@@ -558,7 +558,7 @@
         <v>41759</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.00138481355759764</v>
+        <v>-0.0004882236260403448</v>
       </c>
     </row>
     <row r="17">
@@ -566,7 +566,7 @@
         <v>41790</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.001041686320120928</v>
       </c>
     </row>
     <row r="18">
@@ -574,7 +574,7 @@
         <v>41820</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.0005574067263558502</v>
       </c>
     </row>
     <row r="19">
@@ -582,7 +582,7 @@
         <v>41851</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.001175902576038587</v>
+        <v>-0.003184592813322364</v>
       </c>
     </row>
     <row r="20">
@@ -590,7 +590,7 @@
         <v>41882</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.002726601185508594</v>
       </c>
     </row>
     <row r="21">
@@ -598,7 +598,7 @@
         <v>41912</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-0.002690059503812629</v>
       </c>
     </row>
     <row r="22">
@@ -606,7 +606,7 @@
         <v>41943</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.002727601527541945</v>
+        <v>-0.0009310588369549479</v>
       </c>
     </row>
     <row r="23">
@@ -614,7 +614,7 @@
         <v>41973</v>
       </c>
       <c r="B23" t="n">
-        <v>0.002473235469252915</v>
+        <v>0.003880133258832556</v>
       </c>
     </row>
     <row r="24">
@@ -622,7 +622,7 @@
         <v>42004</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0004661378240420959</v>
+        <v>-0.001402463003770399</v>
       </c>
     </row>
     <row r="25">
@@ -630,7 +630,7 @@
         <v>42035</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.002275160744537534</v>
+        <v>-0.0004720506054531487</v>
       </c>
     </row>
     <row r="26">
@@ -638,7 +638,7 @@
         <v>42063</v>
       </c>
       <c r="B26" t="n">
-        <v>0.005900868884022044</v>
+        <v>0.006943869454561985</v>
       </c>
     </row>
     <row r="27">
@@ -646,7 +646,7 @@
         <v>42094</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.0003502722428037167</v>
       </c>
     </row>
     <row r="28">
@@ -654,7 +654,7 @@
         <v>42124</v>
       </c>
       <c r="B28" t="n">
-        <v>9.238950367328961e-05</v>
+        <v>0.004450009055087601</v>
       </c>
     </row>
     <row r="29">
@@ -662,7 +662,7 @@
         <v>42155</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.00146262492522014</v>
       </c>
     </row>
     <row r="30">
@@ -670,7 +670,7 @@
         <v>42185</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0.002020400481541916</v>
       </c>
     </row>
     <row r="31">
@@ -678,7 +678,7 @@
         <v>42216</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0009518083335967696</v>
+        <v>0.001113695123381632</v>
       </c>
     </row>
     <row r="32">
@@ -686,7 +686,7 @@
         <v>42247</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>-0.003882130388153683</v>
       </c>
     </row>
     <row r="33">
@@ -694,7 +694,7 @@
         <v>42277</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>-0.003243709610228391</v>
       </c>
     </row>
     <row r="34">
@@ -702,7 +702,7 @@
         <v>42308</v>
       </c>
       <c r="B34" t="n">
-        <v>0.001981555580526884</v>
+        <v>0.005252752105660478</v>
       </c>
     </row>
     <row r="35">
@@ -710,7 +710,7 @@
         <v>42338</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>-0.0004382351988738057</v>
       </c>
     </row>
     <row r="36">
@@ -718,7 +718,7 @@
         <v>42369</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>-0.00257895617965294</v>
       </c>
     </row>
     <row r="37">
@@ -726,7 +726,7 @@
         <v>42400</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.002791481397298529</v>
+        <v>-0.009455135462746405</v>
       </c>
     </row>
     <row r="38">
@@ -734,7 +734,7 @@
         <v>42429</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>0.001608666890112789</v>
       </c>
     </row>
     <row r="39">
@@ -742,7 +742,7 @@
         <v>42460</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>0.008367238027009141</v>
       </c>
     </row>
     <row r="40">
@@ -750,7 +750,7 @@
         <v>42490</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0002301625388884053</v>
+        <v>0.002004101731745219</v>
       </c>
     </row>
     <row r="41">
@@ -758,7 +758,7 @@
         <v>42521</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>0.0007935863640779158</v>
       </c>
     </row>
     <row r="42">
@@ -766,7 +766,7 @@
         <v>42551</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>-0.004695661026902389</v>
       </c>
     </row>
     <row r="43">
@@ -774,7 +774,7 @@
         <v>42582</v>
       </c>
       <c r="B43" t="n">
-        <v>0.002571454078953921</v>
+        <v>0.006199169842802565</v>
       </c>
     </row>
     <row r="44">
@@ -782,7 +782,7 @@
         <v>42613</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>0.00280746747094435</v>
       </c>
     </row>
     <row r="45">
@@ -790,7 +790,7 @@
         <v>42643</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>0.0008739872866251324</v>
       </c>
     </row>
     <row r="46">
@@ -798,7 +798,7 @@
         <v>42674</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.0008691004457344398</v>
+        <v>-0.001571008944748438</v>
       </c>
     </row>
     <row r="47">
@@ -806,7 +806,7 @@
         <v>42704</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>0.003196298717450518</v>
       </c>
     </row>
     <row r="48">
@@ -814,7 +814,7 @@
         <v>42735</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>0.003979937534913282</v>
       </c>
     </row>
     <row r="49">
@@ -822,7 +822,7 @@
         <v>42766</v>
       </c>
       <c r="B49" t="n">
-        <v>0.001664680352085855</v>
+        <v>0.00471544135265666</v>
       </c>
     </row>
     <row r="50">
@@ -830,7 +830,7 @@
         <v>42794</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0006257439369877003</v>
+        <v>0.005167038017633353</v>
       </c>
     </row>
     <row r="51">
@@ -838,7 +838,7 @@
         <v>42825</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>0.002184590112058248</v>
       </c>
     </row>
     <row r="52">
@@ -846,7 +846,7 @@
         <v>42855</v>
       </c>
       <c r="B52" t="n">
-        <v>0.0007276492000771467</v>
+        <v>0.001950549130911966</v>
       </c>
     </row>
     <row r="53">
@@ -854,7 +854,7 @@
         <v>42886</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0004821268660174517</v>
+        <v>0.003704507003489468</v>
       </c>
     </row>
     <row r="54">
@@ -862,7 +862,7 @@
         <v>42916</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>0.0006190666020128486</v>
       </c>
     </row>
     <row r="55">
@@ -870,7 +870,7 @@
         <v>42947</v>
       </c>
       <c r="B55" t="n">
-        <v>0.0008326604166612064</v>
+        <v>0.004876493638910784</v>
       </c>
     </row>
     <row r="56">
@@ -878,7 +878,7 @@
         <v>42978</v>
       </c>
       <c r="B56" t="n">
-        <v>0.0003437550559138694</v>
+        <v>0.001006166792368421</v>
       </c>
     </row>
     <row r="57">
@@ -886,7 +886,7 @@
         <v>43008</v>
       </c>
       <c r="B57" t="n">
-        <v>0.0009461175462728278</v>
+        <v>0.004129471563751397</v>
       </c>
     </row>
     <row r="58">
@@ -894,7 +894,7 @@
         <v>43039</v>
       </c>
       <c r="B58" t="n">
-        <v>0.0009143330289407293</v>
+        <v>0.0006522847296856309</v>
       </c>
     </row>
     <row r="59">
@@ -902,7 +902,7 @@
         <v>43069</v>
       </c>
       <c r="B59" t="n">
-        <v>0.002692066205806687</v>
+        <v>0.00153465269126071</v>
       </c>
     </row>
     <row r="60">
@@ -910,7 +910,7 @@
         <v>43100</v>
       </c>
       <c r="B60" t="n">
-        <v>-6.029599405382353e-06</v>
+        <v>0.0003783133110789932</v>
       </c>
     </row>
     <row r="61">
@@ -918,7 +918,7 @@
         <v>43131</v>
       </c>
       <c r="B61" t="n">
-        <v>0.001555279656052503</v>
+        <v>0.00461579244823954</v>
       </c>
     </row>
     <row r="62">
@@ -926,7 +926,7 @@
         <v>43159</v>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>-0.00296689842152868</v>
       </c>
     </row>
     <row r="63">
@@ -934,7 +934,7 @@
         <v>43190</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>-0.002445653029737285</v>
       </c>
     </row>
     <row r="64">
@@ -942,7 +942,7 @@
         <v>43220</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.0005910304996390869</v>
+        <v>0.0001057668296193021</v>
       </c>
     </row>
     <row r="65">
@@ -950,7 +950,7 @@
         <v>43251</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>-0.001193645458025317</v>
       </c>
     </row>
     <row r="66">
@@ -958,7 +958,7 @@
         <v>43281</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>0.000503934949780636</v>
       </c>
     </row>
     <row r="67">
@@ -966,7 +966,7 @@
         <v>43312</v>
       </c>
       <c r="B67" t="n">
-        <v>0.0008540417604828783</v>
+        <v>0.0006944842691797634</v>
       </c>
     </row>
     <row r="68">
@@ -974,7 +974,7 @@
         <v>43343</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>-0.0005743209525756331</v>
       </c>
     </row>
     <row r="69">
@@ -982,7 +982,7 @@
         <v>43373</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>0.0004682888056149804</v>
       </c>
     </row>
     <row r="70">
@@ -990,7 +990,7 @@
         <v>43404</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.0014259772346083</v>
+        <v>-0.007548522436377778</v>
       </c>
     </row>
     <row r="71">
@@ -998,7 +998,7 @@
         <v>43434</v>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>-0.0007617429906892563</v>
       </c>
     </row>
     <row r="72">
@@ -1006,7 +1006,7 @@
         <v>43465</v>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>-0.006966138839686483</v>
       </c>
     </row>
     <row r="73">
@@ -1014,7 +1014,7 @@
         <v>43496</v>
       </c>
       <c r="B73" t="n">
-        <v>0.002694730956766983</v>
+        <v>0.009747005983749306</v>
       </c>
     </row>
     <row r="74">
@@ -1022,7 +1022,7 @@
         <v>43524</v>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>0.005681350034502814</v>
       </c>
     </row>
     <row r="75">
@@ -1030,7 +1030,7 @@
         <v>43555</v>
       </c>
       <c r="B75" t="n">
-        <v>0.001177609045681055</v>
+        <v>-0.000630455941160805</v>
       </c>
     </row>
     <row r="76">
@@ -1038,7 +1038,7 @@
         <v>43585</v>
       </c>
       <c r="B76" t="n">
-        <v>0.00140362724460402</v>
+        <v>0.003391656904738798</v>
       </c>
     </row>
     <row r="77">
@@ -1046,7 +1046,7 @@
         <v>43616</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>-0.007418048448013061</v>
       </c>
     </row>
     <row r="78">
@@ -1054,7 +1054,7 @@
         <v>43646</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>0.006897330046136928</v>
       </c>
     </row>
     <row r="79">
@@ -1062,7 +1062,7 @@
         <v>43677</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0002514198012653968</v>
+        <v>0.002614272373831268</v>
       </c>
     </row>
     <row r="80">
@@ -1070,7 +1070,7 @@
         <v>43708</v>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>-0.004007452069296331</v>
       </c>
     </row>
     <row r="81">
@@ -1078,7 +1078,7 @@
         <v>43738</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>0.004680780169768015</v>
       </c>
     </row>
     <row r="82">
@@ -1086,7 +1086,7 @@
         <v>43769</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0009030676363967058</v>
+        <v>0.002337552888943068</v>
       </c>
     </row>
     <row r="83">
@@ -1094,7 +1094,7 @@
         <v>43799</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>0.004025695172958015</v>
       </c>
     </row>
     <row r="84">
@@ -1102,7 +1102,7 @@
         <v>43830</v>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>0.00310566073272524</v>
       </c>
     </row>
     <row r="85">
@@ -1110,7 +1110,7 @@
         <v>43861</v>
       </c>
       <c r="B85" t="n">
-        <v>3.525431608342731e-05</v>
+        <v>0.0003967025668916547</v>
       </c>
     </row>
     <row r="86">
@@ -1118,7 +1118,7 @@
         <v>43890</v>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>-0.009859687199706247</v>
       </c>
     </row>
     <row r="87">
@@ -1126,7 +1126,7 @@
         <v>43921</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>-0.01693104221479366</v>
       </c>
     </row>
     <row r="88">
@@ -1134,7 +1134,7 @@
         <v>43951</v>
       </c>
       <c r="B88" t="n">
-        <v>0.002411027941928178</v>
+        <v>0.01734805229320634</v>
       </c>
     </row>
     <row r="89">
@@ -1142,7 +1142,7 @@
         <v>43982</v>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>0.006818550951268635</v>
       </c>
     </row>
     <row r="90">
@@ -1150,7 +1150,7 @@
         <v>44012</v>
       </c>
       <c r="B90" t="n">
-        <v>0.005284723465446721</v>
+        <v>0.005781448636716062</v>
       </c>
     </row>
     <row r="91">
@@ -1158,7 +1158,7 @@
         <v>44043</v>
       </c>
       <c r="B91" t="n">
-        <v>0.00450942680492215</v>
+        <v>0.004990521330494564</v>
       </c>
     </row>
     <row r="92">
@@ -1166,7 +1166,7 @@
         <v>44074</v>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>0.004488371632808201</v>
       </c>
     </row>
     <row r="93">
@@ -1174,7 +1174,7 @@
         <v>44104</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>-0.002547282505611131</v>
       </c>
     </row>
     <row r="94">
@@ -1182,7 +1182,7 @@
         <v>44135</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.001256106868246381</v>
+        <v>-0.002775138229323116</v>
       </c>
     </row>
     <row r="95">
@@ -1190,7 +1190,7 @@
         <v>44165</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>0.01837999556501554</v>
       </c>
     </row>
     <row r="96">
@@ -1198,7 +1198,7 @@
         <v>44196</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>0.005319909524146918</v>
       </c>
     </row>
     <row r="97">
@@ -1206,7 +1206,7 @@
         <v>44227</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.0005277260550679002</v>
+        <v>0.0009810385825841474</v>
       </c>
     </row>
     <row r="98">
@@ -1214,7 +1214,7 @@
         <v>44255</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>0.006392141731224831</v>
       </c>
     </row>
     <row r="99">
@@ -1222,7 +1222,7 @@
         <v>44286</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>0.004751772735293249</v>
       </c>
     </row>
     <row r="100">
@@ -1230,7 +1230,7 @@
         <v>44316</v>
       </c>
       <c r="B100" t="n">
-        <v>0.0004653869778174627</v>
+        <v>0.002061663216096068</v>
       </c>
     </row>
     <row r="101">
@@ -1238,7 +1238,7 @@
         <v>44347</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>0.003625605582075498</v>
       </c>
     </row>
     <row r="102">
@@ -1246,7 +1246,7 @@
         <v>44377</v>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>-0.0009578539029881995</v>
       </c>
     </row>
     <row r="103">
@@ -1254,7 +1254,7 @@
         <v>44408</v>
       </c>
       <c r="B103" t="n">
-        <v>0.0005348124795830639</v>
+        <v>-0.0033746450410843</v>
       </c>
     </row>
     <row r="104">
@@ -1262,7 +1262,7 @@
         <v>44439</v>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>0.003468547652345077</v>
       </c>
     </row>
     <row r="105">
@@ -1270,7 +1270,7 @@
         <v>44469</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>-0.002670199241254517</v>
       </c>
     </row>
     <row r="106">
@@ -1278,7 +1278,7 @@
         <v>44500</v>
       </c>
       <c r="B106" t="n">
-        <v>0.001701725234082771</v>
+        <v>0.0004077258618800286</v>
       </c>
     </row>
     <row r="107">
@@ -1286,7 +1286,7 @@
         <v>44530</v>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>-0.004565336948677572</v>
       </c>
     </row>
     <row r="108">
@@ -1294,7 +1294,7 @@
         <v>44561</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>0.006982692120436127</v>
       </c>
     </row>
     <row r="109">
@@ -1302,7 +1302,7 @@
         <v>44592</v>
       </c>
       <c r="B109" t="n">
-        <v>-0.001743942330466818</v>
+        <v>-0.002789803145129749</v>
       </c>
     </row>
     <row r="110">
@@ -1310,7 +1310,7 @@
         <v>44620</v>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>-0.002453267530260727</v>
       </c>
     </row>
     <row r="111">
@@ -1318,7 +1318,7 @@
         <v>44651</v>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>0.00325256983765454</v>
       </c>
     </row>
     <row r="112">
@@ -1326,7 +1326,7 @@
         <v>44681</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.001062362371294637</v>
+        <v>-0.006553709645996379</v>
       </c>
     </row>
     <row r="113">
@@ -1334,7 +1334,7 @@
         <v>44712</v>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>0.001433200839993905</v>
       </c>
     </row>
     <row r="114">
@@ -1342,7 +1342,7 @@
         <v>44742</v>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>-0.01172237090442355</v>
       </c>
     </row>
     <row r="115">
@@ -1350,7 +1350,7 @@
         <v>44773</v>
       </c>
       <c r="B115" t="n">
-        <v>0.002363823028106078</v>
+        <v>0.01057540894572015</v>
       </c>
     </row>
     <row r="116">
@@ -1358,7 +1358,7 @@
         <v>44804</v>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>-0.003246817330126493</v>
       </c>
     </row>
     <row r="117">
@@ -1366,7 +1366,7 @@
         <v>44834</v>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>-0.008297920289607307</v>
       </c>
     </row>
     <row r="118">
@@ -1374,7 +1374,7 @@
         <v>44865</v>
       </c>
       <c r="B118" t="n">
-        <v>0.003505037987519152</v>
+        <v>0.01567301503004542</v>
       </c>
     </row>
     <row r="119">
@@ -1382,7 +1382,7 @@
         <v>44895</v>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>0.011913114236258</v>
       </c>
     </row>
     <row r="120">
@@ -1390,7 +1390,7 @@
         <v>44926</v>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>-0.002107603053654497</v>
       </c>
     </row>
     <row r="121">
@@ -1398,7 +1398,7 @@
         <v>44957</v>
       </c>
       <c r="B121" t="n">
-        <v>0.002960255277207511</v>
+        <v>0.01349099556600592</v>
       </c>
     </row>
     <row r="122">
@@ -1406,7 +1406,7 @@
         <v>44985</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>-0.001584566007583001</v>
       </c>
     </row>
     <row r="123">
@@ -1414,7 +1414,7 @@
         <v>45016</v>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>-0.0001577958141125531</v>
       </c>
     </row>
     <row r="124">
@@ -1422,7 +1422,7 @@
         <v>45046</v>
       </c>
       <c r="B124" t="n">
-        <v>0.0008975522917683841</v>
+        <v>-0.001185508566042713</v>
       </c>
     </row>
     <row r="125">
@@ -1430,7 +1430,7 @@
         <v>45077</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>-0.002267936966916607</v>
       </c>
     </row>
     <row r="126">
@@ -1438,7 +1438,7 @@
         <v>45107</v>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>0.006211376036453782</v>
       </c>
     </row>
     <row r="127">
@@ -1446,7 +1446,7 @@
         <v>45138</v>
       </c>
       <c r="B127" t="n">
-        <v>0.0009309131155126528</v>
+        <v>0.005042315513268596</v>
       </c>
     </row>
     <row r="128">
@@ -1454,7 +1454,7 @@
         <v>45169</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>-0.002784459008039621</v>
       </c>
     </row>
     <row r="129">
@@ -1462,7 +1462,7 @@
         <v>45199</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>-0.006004577903281553</v>
       </c>
     </row>
     <row r="130">
@@ -1470,7 +1470,7 @@
         <v>45230</v>
       </c>
       <c r="B130" t="n">
-        <v>-0.002108613610004985</v>
+        <v>-0.008737832289355643</v>
       </c>
     </row>
     <row r="131">
@@ -1478,7 +1478,7 @@
         <v>45260</v>
       </c>
       <c r="B131" t="n">
-        <v>0.0004767869985814667</v>
+        <v>0.01142333626202555</v>
       </c>
     </row>
     <row r="132">
@@ -1486,7 +1486,7 @@
         <v>45291</v>
       </c>
       <c r="B132" t="n">
-        <v>0.004127452090353234</v>
+        <v>0.003365101187823908</v>
       </c>
     </row>
     <row r="133">
@@ -1494,7 +1494,7 @@
         <v>45322</v>
       </c>
       <c r="B133" t="n">
-        <v>0.0005635933722142772</v>
+        <v>0.0001318619997788035</v>
       </c>
     </row>
     <row r="134">
@@ -1502,7 +1502,7 @@
         <v>45351</v>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>0.001565041830608065</v>
       </c>
     </row>
     <row r="135">
@@ -1510,7 +1510,7 @@
         <v>45382</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>0.002586205121286455</v>
       </c>
     </row>
     <row r="136">
@@ -1518,7 +1518,7 @@
         <v>45412</v>
       </c>
       <c r="B136" t="n">
-        <v>-0.0009861235775864403</v>
+        <v>-0.003858587783503757</v>
       </c>
     </row>
     <row r="137">
@@ -1526,7 +1526,7 @@
         <v>45443</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>0.001574021251727816</v>
       </c>
     </row>
     <row r="138">
@@ -1534,7 +1534,7 @@
         <v>45473</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>0.0004209739901591461</v>
       </c>
     </row>
     <row r="139">
@@ -1542,7 +1542,7 @@
         <v>45504</v>
       </c>
       <c r="B139" t="n">
-        <v>0.0001586032474507261</v>
+        <v>-0.0007880902917137354</v>
       </c>
     </row>
     <row r="140">
@@ -1550,7 +1550,7 @@
         <v>45535</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>0.003670067844600182</v>
       </c>
     </row>
     <row r="141">
@@ -1558,7 +1558,7 @@
         <v>45565</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>0.002698395599144366</v>
       </c>
     </row>
     <row r="142">
@@ -1566,7 +1566,7 @@
         <v>45596</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.002870916892509833</v>
+        <v>-0.003204404514372242</v>
       </c>
     </row>
     <row r="143">
@@ -1574,7 +1574,7 @@
         <v>45626</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>0.0005114816571303463</v>
       </c>
     </row>
     <row r="144">
@@ -1582,7 +1582,7 @@
         <v>45657</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>-0.003162931091731539</v>
       </c>
     </row>
     <row r="145">
@@ -1590,7 +1590,7 @@
         <v>45688</v>
       </c>
       <c r="B145" t="n">
-        <v>-8.802776601805505e-05</v>
+        <v>0.004090349074945928</v>
       </c>
     </row>
     <row r="146">
@@ -1598,7 +1598,7 @@
         <v>45716</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>0.0006092887123389757</v>
       </c>
     </row>
     <row r="147">
@@ -1606,7 +1606,7 @@
         <v>45747</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>-0.001812718485247951</v>
       </c>
     </row>
   </sheetData>
